--- a/data/trans_dic/P62A$invalidez-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P62A$invalidez-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de invalidez</t>
+          <t>Población que, al menos, percibe una pensión de invalidez (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,22</t>
+          <t>6,29; 11,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 14,26</t>
+          <t>8,73; 14,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,38</t>
+          <t>2,95; 7,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,23</t>
+          <t>1,01; 4,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,68</t>
+          <t>4,1; 8,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,87</t>
+          <t>4,75; 8,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,11</t>
+          <t>3,44; 8,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,65; 56,67</t>
+          <t>49,43; 57,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,15</t>
+          <t>5,78; 9,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,22; 10,81</t>
+          <t>7,21; 10,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 6,87</t>
+          <t>3,55; 6,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,01; 32,94</t>
+          <t>27,88; 33,52</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 20,8</t>
+          <t>9,99; 21,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,75; 32,25</t>
+          <t>20,94; 32,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,05; 19,71</t>
+          <t>12,27; 20,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,38</t>
+          <t>0,39; 2,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,05; 28,84</t>
+          <t>10,98; 28,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,28; 28,82</t>
+          <t>15,55; 29,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 15,69</t>
+          <t>7,17; 15,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 29,59</t>
+          <t>6,22; 29,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,0; 21,7</t>
+          <t>11,94; 21,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,44; 29,13</t>
+          <t>20,25; 29,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,14; 16,63</t>
+          <t>11,11; 16,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 12,96</t>
+          <t>4,73; 13,01</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 15,47</t>
+          <t>2,5; 17,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 35,58</t>
+          <t>7,25; 33,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 16,43</t>
+          <t>2,95; 16,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 21,34</t>
+          <t>2,48; 23,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 32,46</t>
+          <t>5,41; 31,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 16,37</t>
+          <t>1,9; 18,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 17,45</t>
+          <t>4,69; 17,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 15,77</t>
+          <t>3,63; 16,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 28,78</t>
+          <t>9,78; 28,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 14,0</t>
+          <t>4,48; 13,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,57</t>
+          <t>2,49; 8,11</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,21</t>
+          <t>7,73; 12,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 19,17</t>
+          <t>13,71; 19,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 11,96</t>
+          <t>7,93; 12,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,42</t>
+          <t>0,84; 2,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,58</t>
+          <t>6,11; 10,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 13,23</t>
+          <t>8,3; 13,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 9,28</t>
+          <t>5,46; 9,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,83; 40,09</t>
+          <t>15,12; 40,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 10,81</t>
+          <t>7,66; 10,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,87; 15,64</t>
+          <t>11,85; 15,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 10,38</t>
+          <t>7,41; 10,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,69; 20,0</t>
+          <t>11,95; 20,04</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de invalidez</t>
+          <t>Población que, al menos, percibe una pensión de invalidez (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32466; 57286</t>
+          <t>32136; 56868</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46922; 78261</t>
+          <t>47930; 78303</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13319; 32507</t>
+          <t>12981; 32585</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2721; 12631</t>
+          <t>3024; 12785</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18353; 39037</t>
+          <t>18463; 39419</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25064; 47627</t>
+          <t>25501; 48147</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13923; 34504</t>
+          <t>14640; 34702</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>187478; 213952</t>
+          <t>186639; 215230</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54965; 87923</t>
+          <t>55472; 87154</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78399; 117340</t>
+          <t>78312; 118693</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31527; 59463</t>
+          <t>30727; 56959</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>189489; 222845</t>
+          <t>188561; 226738</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16708; 34659</t>
+          <t>16655; 35290</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57163; 88842</t>
+          <t>57683; 89218</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46709; 76371</t>
+          <t>47564; 78856</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1526; 9339</t>
+          <t>1522; 9788</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9395; 24514</t>
+          <t>9333; 24188</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26080; 49179</t>
+          <t>26533; 50975</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18888; 40378</t>
+          <t>18457; 40088</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23712; 143112</t>
+          <t>30095; 142007</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30199; 54595</t>
+          <t>30034; 54427</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91205; 129935</t>
+          <t>90358; 131075</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71868; 107267</t>
+          <t>71636; 108394</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39395; 113523</t>
+          <t>41389; 113951</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>919; 9385</t>
+          <t>1517; 10351</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3363; 16234</t>
+          <t>3308; 15213</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2038; 11385</t>
+          <t>2043; 11716</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3925</t>
+          <t>0; 4190</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1020; 8799</t>
+          <t>1022; 9642</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2003; 11546</t>
+          <t>1926; 11262</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>985; 8642</t>
+          <t>1003; 9527</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3523; 12907</t>
+          <t>3469; 13200</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4158; 16070</t>
+          <t>3698; 16358</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7969; 23369</t>
+          <t>7939; 22863</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4942; 17091</t>
+          <t>5468; 17059</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4269; 15625</t>
+          <t>4532; 14783</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>56950; 90081</t>
+          <t>57073; 90981</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>121586; 166805</t>
+          <t>119292; 166641</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69692; 107352</t>
+          <t>71148; 108551</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6409; 19340</t>
+          <t>6700; 18370</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34552; 60976</t>
+          <t>35221; 63012</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>63130; 98274</t>
+          <t>61657; 97070</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39525; 68287</t>
+          <t>40155; 70075</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>157386; 374948</t>
+          <t>141369; 374352</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>101582; 142040</t>
+          <t>100677; 140889</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>191483; 252285</t>
+          <t>191108; 250319</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>120265; 169523</t>
+          <t>120952; 169066</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>202838; 346862</t>
+          <t>207204; 347644</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$invalidez-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P62A$invalidez-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 11,14</t>
+          <t>6,33; 11,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,73; 14,26</t>
+          <t>8,46; 14,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,4</t>
+          <t>3,18; 7,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,28</t>
+          <t>0,96; 4,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,76</t>
+          <t>4,24; 8,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,97</t>
+          <t>4,75; 9,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,16</t>
+          <t>3,12; 7,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,43; 57,0</t>
+          <t>49,19; 56,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,07</t>
+          <t>5,81; 9,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,93</t>
+          <t>7,38; 11,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,58</t>
+          <t>3,53; 6,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,88; 33,52</t>
+          <t>28,05; 33,29</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 21,18</t>
+          <t>10,22; 21,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,94; 32,39</t>
+          <t>21,63; 32,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,27; 20,35</t>
+          <t>11,88; 19,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,5</t>
+          <t>0,35; 2,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,98; 28,46</t>
+          <t>11,22; 29,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,55; 29,87</t>
+          <t>14,85; 29,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 15,58</t>
+          <t>7,02; 15,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,22; 29,36</t>
+          <t>23,75; 32,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 21,63</t>
+          <t>11,83; 21,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,25; 29,38</t>
+          <t>20,14; 29,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,11; 16,81</t>
+          <t>10,95; 16,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 13,01</t>
+          <t>10,5; 14,36</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 17,06</t>
+          <t>2,5; 17,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 33,34</t>
+          <t>9,06; 35,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 16,91</t>
+          <t>2,99; 17,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 23,38</t>
+          <t>2,5; 25,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 31,66</t>
+          <t>5,58; 34,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 18,05</t>
+          <t>1,85; 17,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 17,84</t>
+          <t>4,51; 16,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 16,05</t>
+          <t>3,67; 14,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 28,16</t>
+          <t>9,66; 30,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 13,97</t>
+          <t>4,11; 14,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,11</t>
+          <t>1,99; 7,0</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,33</t>
+          <t>7,89; 12,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,71; 19,15</t>
+          <t>13,86; 19,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,1</t>
+          <t>7,9; 12,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,3</t>
+          <t>0,75; 2,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,94</t>
+          <t>6,18; 10,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 13,07</t>
+          <t>8,42; 13,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,53</t>
+          <t>5,6; 9,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,12; 40,03</t>
+          <t>35,85; 41,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 10,72</t>
+          <t>7,56; 10,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,85; 15,52</t>
+          <t>12,03; 15,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 10,35</t>
+          <t>7,43; 10,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,95; 20,04</t>
+          <t>17,84; 20,8</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>200630</t>
+          <t>216991</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>206797</t>
+          <t>223500</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32136; 56868</t>
+          <t>32315; 57575</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47930; 78303</t>
+          <t>46451; 78087</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12981; 32585</t>
+          <t>13997; 32237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3024; 12785</t>
+          <t>3087; 13329</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18463; 39419</t>
+          <t>19092; 37838</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25501; 48147</t>
+          <t>25516; 48619</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14640; 34702</t>
+          <t>13288; 33860</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>186639; 215230</t>
+          <t>202202; 232887</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55472; 87154</t>
+          <t>55805; 88576</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>78312; 118693</t>
+          <t>80156; 121033</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30727; 56959</t>
+          <t>30600; 58419</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>188561; 226738</t>
+          <t>205287; 243670</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>79018</t>
+          <t>84967</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83164</t>
+          <t>89255</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16655; 35290</t>
+          <t>17034; 35566</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57683; 89218</t>
+          <t>59584; 90289</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47564; 78856</t>
+          <t>46045; 77321</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1522; 9788</t>
+          <t>1514; 9766</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9333; 24188</t>
+          <t>9534; 25296</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26533; 50975</t>
+          <t>25340; 49653</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18457; 40088</t>
+          <t>18071; 39573</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30095; 142007</t>
+          <t>72359; 97926</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30034; 54427</t>
+          <t>29774; 53788</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90358; 131075</t>
+          <t>89828; 130841</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71636; 108394</t>
+          <t>70608; 107870</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41389; 113951</t>
+          <t>76895; 105199</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>8296</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1517; 10351</t>
+          <t>1518; 10876</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3308; 15213</t>
+          <t>4134; 16393</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2043; 11716</t>
+          <t>2071; 11824</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4190</t>
+          <t>0; 4842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1022; 9642</t>
+          <t>1031; 10440</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1926; 11262</t>
+          <t>1985; 12406</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1003; 9527</t>
+          <t>975; 9364</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3469; 13200</t>
+          <t>3863; 14032</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3698; 16358</t>
+          <t>3739; 15201</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7939; 22863</t>
+          <t>7846; 24675</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5468; 17059</t>
+          <t>5017; 17209</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4532; 14783</t>
+          <t>4159; 14607</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>286750</t>
+          <t>309410</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>297898</t>
+          <t>321051</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57073; 90981</t>
+          <t>58227; 90227</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>119292; 166641</t>
+          <t>120614; 166691</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71148; 108551</t>
+          <t>70893; 110156</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6700; 18370</t>
+          <t>6553; 20364</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35221; 63012</t>
+          <t>35608; 60881</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61657; 97070</t>
+          <t>62531; 97179</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40155; 70075</t>
+          <t>41161; 71652</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>141369; 374352</t>
+          <t>287312; 331601</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100677; 140889</t>
+          <t>99271; 142305</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>191108; 250319</t>
+          <t>194062; 253429</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>120952; 169066</t>
+          <t>121363; 166381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>207204; 347644</t>
+          <t>298475; 348021</t>
         </is>
       </c>
     </row>
